--- a/Task-9/CoffeeShop_Sales.xlsx
+++ b/Task-9/CoffeeShop_Sales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nada\Documents\IEEE-CS-DataScience-26\Task-9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489FC56C-8F96-4F5C-B3AF-BB631E5152DF}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68288A48-336D-4A8E-B100-7B901ED99AD3}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{47E50953-5618-481F-96AD-69ADE76811E8}"/>
   </bookViews>
